--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.31092123792253</v>
+        <v>5.575524701162411</v>
       </c>
       <c r="D2" t="n">
-        <v>26.41441341443964</v>
+        <v>4.292342179846441</v>
       </c>
       <c r="E2" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F2" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.20053395181375</v>
+        <v>5.232586767169734</v>
       </c>
       <c r="D3" t="n">
-        <v>32.26960588382232</v>
+        <v>5.243810956121126</v>
       </c>
       <c r="E3" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F3" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.58609380480358</v>
+        <v>2.532740243280581</v>
       </c>
       <c r="D4" t="n">
-        <v>15.88240182539703</v>
+        <v>2.580890296627018</v>
       </c>
       <c r="E4" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F4" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.78446167606799</v>
+        <v>5.977475022361049</v>
       </c>
       <c r="D5" t="n">
-        <v>36.02431335463479</v>
+        <v>5.853950920128154</v>
       </c>
       <c r="E5" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F5" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.80798490812692</v>
+        <v>4.681297547570625</v>
       </c>
       <c r="D6" t="n">
-        <v>28.29723257364903</v>
+        <v>4.598300293217967</v>
       </c>
       <c r="E6" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F6" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.99273625905093</v>
+        <v>3.411319642095777</v>
       </c>
       <c r="D7" t="n">
-        <v>19.84626990788189</v>
+        <v>3.225018860030807</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F7" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.09991273117072</v>
+        <v>2.291235818815242</v>
       </c>
       <c r="D8" t="n">
-        <v>11.67261752992875</v>
+        <v>1.896800348613422</v>
       </c>
       <c r="E8" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F8" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.77525236829771</v>
+        <v>6.463478509848378</v>
       </c>
       <c r="D9" t="n">
-        <v>38.45037055623263</v>
+        <v>6.248185215387803</v>
       </c>
       <c r="E9" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F9" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4.261397917457984</v>
+        <v>0.6924771615869224</v>
       </c>
       <c r="D10" t="n">
-        <v>5.661385479594928</v>
+        <v>0.9199751404341758</v>
       </c>
       <c r="E10" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F10" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.176524765932976</v>
+        <v>1.166185274464109</v>
       </c>
       <c r="D11" t="n">
-        <v>25.48038461248181</v>
+        <v>4.140562499528295</v>
       </c>
       <c r="E11" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F11" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.91144792966907</v>
+        <v>4.860610288571224</v>
       </c>
       <c r="D12" t="n">
-        <v>19.91105220725414</v>
+        <v>3.235545983678798</v>
       </c>
       <c r="E12" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F12" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.18426504232175</v>
+        <v>6.854943069377286</v>
       </c>
       <c r="D13" t="n">
-        <v>41.0424581540529</v>
+        <v>6.669399450033596</v>
       </c>
       <c r="E13" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F13" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.27863250849325</v>
+        <v>6.382777782630153</v>
       </c>
       <c r="D14" t="n">
-        <v>22.76906305595352</v>
+        <v>3.699972746592448</v>
       </c>
       <c r="E14" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F14" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>11.87221642245511</v>
+        <v>1.929235168648956</v>
       </c>
       <c r="D15" t="n">
-        <v>12.86585052783814</v>
+        <v>2.090700710773697</v>
       </c>
       <c r="E15" t="n">
-        <v>12.45957362482634</v>
+        <v>2.02468071403428</v>
       </c>
       <c r="F15" t="n">
-        <v>10.18512070461225</v>
+        <v>1.65508211449949</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
